--- a/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0003T0006Z000C1N20_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0003T0006Z000C1N20_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>42.34345894807068</v>
+        <v>6.880812079061485</v>
       </c>
       <c r="D2" t="n">
-        <v>42.49431835917304</v>
+        <v>6.905326733365619</v>
       </c>
       <c r="E2" t="n">
-        <v>10.62229984244127</v>
+        <v>1.726123724396706</v>
       </c>
       <c r="F2" t="n">
-        <v>10.81533233218629</v>
+        <v>1.757491503980271</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>10.80743137192987</v>
+        <v>1.756207597938603</v>
       </c>
       <c r="D3" t="n">
-        <v>10.50130076512563</v>
+        <v>1.706461374332915</v>
       </c>
       <c r="E3" t="n">
-        <v>10.62229984244127</v>
+        <v>1.726123724396706</v>
       </c>
       <c r="F3" t="n">
-        <v>10.81533233218629</v>
+        <v>1.757491503980271</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>39.77485828187506</v>
+        <v>6.463414470804698</v>
       </c>
       <c r="D4" t="n">
-        <v>39.10479955665858</v>
+        <v>6.354529927957019</v>
       </c>
       <c r="E4" t="n">
-        <v>10.62229984244127</v>
+        <v>1.726123724396706</v>
       </c>
       <c r="F4" t="n">
-        <v>10.81533233218629</v>
+        <v>1.757491503980271</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>30.5639165075319</v>
+        <v>4.966636432473934</v>
       </c>
       <c r="D5" t="n">
-        <v>30.08048541337382</v>
+        <v>4.888078879673246</v>
       </c>
       <c r="E5" t="n">
-        <v>10.62229984244127</v>
+        <v>1.726123724396706</v>
       </c>
       <c r="F5" t="n">
-        <v>10.81533233218629</v>
+        <v>1.757491503980271</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>27.85847887942897</v>
+        <v>4.527002817907208</v>
       </c>
       <c r="D6" t="n">
-        <v>27.1392594290775</v>
+        <v>4.410129657225093</v>
       </c>
       <c r="E6" t="n">
-        <v>10.62229984244127</v>
+        <v>1.726123724396706</v>
       </c>
       <c r="F6" t="n">
-        <v>10.81533233218629</v>
+        <v>1.757491503980271</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>31.7024896516602</v>
+        <v>5.151654568394783</v>
       </c>
       <c r="D7" t="n">
-        <v>30.95466413210336</v>
+        <v>5.030132921466796</v>
       </c>
       <c r="E7" t="n">
-        <v>10.62229984244127</v>
+        <v>1.726123724396706</v>
       </c>
       <c r="F7" t="n">
-        <v>10.81533233218629</v>
+        <v>1.757491503980271</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>21.45090174010153</v>
+        <v>3.485771532766499</v>
       </c>
       <c r="D8" t="n">
-        <v>21.04649449906493</v>
+        <v>3.420055356098052</v>
       </c>
       <c r="E8" t="n">
-        <v>10.62229984244127</v>
+        <v>1.726123724396706</v>
       </c>
       <c r="F8" t="n">
-        <v>10.81533233218629</v>
+        <v>1.757491503980271</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>43.47751344758934</v>
+        <v>7.065095935233268</v>
       </c>
       <c r="D9" t="n">
-        <v>43.18807196513403</v>
+        <v>7.01806169433428</v>
       </c>
       <c r="E9" t="n">
-        <v>10.62229984244127</v>
+        <v>1.726123724396706</v>
       </c>
       <c r="F9" t="n">
-        <v>10.81533233218629</v>
+        <v>1.757491503980271</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>31.06374563850265</v>
+        <v>5.047858666256681</v>
       </c>
       <c r="D10" t="n">
-        <v>31.10383454346668</v>
+        <v>5.054373113313335</v>
       </c>
       <c r="E10" t="n">
-        <v>10.62229984244127</v>
+        <v>1.726123724396706</v>
       </c>
       <c r="F10" t="n">
-        <v>10.81533233218629</v>
+        <v>1.757491503980271</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>38.62618528596855</v>
+        <v>6.276755108969891</v>
       </c>
       <c r="D11" t="n">
-        <v>39.37847933576377</v>
+        <v>6.399002892061613</v>
       </c>
       <c r="E11" t="n">
-        <v>10.62229984244127</v>
+        <v>1.726123724396706</v>
       </c>
       <c r="F11" t="n">
-        <v>10.81533233218629</v>
+        <v>1.757491503980271</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>41.23167538278154</v>
+        <v>6.700147249702001</v>
       </c>
       <c r="D12" t="n">
-        <v>41.37907463708943</v>
+        <v>6.724099628527033</v>
       </c>
       <c r="E12" t="n">
-        <v>10.62229984244127</v>
+        <v>1.726123724396706</v>
       </c>
       <c r="F12" t="n">
-        <v>10.81533233218629</v>
+        <v>1.757491503980271</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>49.21727519068578</v>
+        <v>7.99780721848644</v>
       </c>
       <c r="D13" t="n">
-        <v>49.82896473681252</v>
+        <v>8.097206769732034</v>
       </c>
       <c r="E13" t="n">
-        <v>10.62229984244127</v>
+        <v>1.726123724396706</v>
       </c>
       <c r="F13" t="n">
-        <v>10.81533233218629</v>
+        <v>1.757491503980271</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>18.92731628933916</v>
+        <v>3.075688897017614</v>
       </c>
       <c r="D14" t="n">
-        <v>18.9746551967247</v>
+        <v>3.083381469467764</v>
       </c>
       <c r="E14" t="n">
-        <v>10.62229984244127</v>
+        <v>1.726123724396706</v>
       </c>
       <c r="F14" t="n">
-        <v>10.81533233218629</v>
+        <v>1.757491503980271</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
